--- a/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
+++ b/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
@@ -1057,16 +1057,18 @@
           <t>Apparent current L1 N</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n"/>
+      <c r="B2" s="5" t="n">
+        <v>670</v>
+      </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Float32 (ABCD)</t>
         </is>
       </c>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>SAU-100 electric meter (LV PV panel)</t>
+          <t>Plant PC data collector (Modbus TCP server, read-only)</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -1076,17 +1078,15 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>192.168.0.128:502</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>TBC (meter address on SAU)</t>
-        </is>
+          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Holding (FC03), 2 regs</t>
         </is>
       </c>
       <c r="J2" s="8" t="inlineStr">
@@ -1094,14 +1094,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+      <c r="K2" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Ready — quality register 1290</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
@@ -1116,10 +1114,12 @@
           <t>Apparent current L2 N</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
+      <c r="B3" s="5" t="n">
+        <v>672</v>
+      </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Float32 (ABCD)</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>SAU-100 electric meter (LV PV panel)</t>
+          <t>Plant PC data collector (Modbus TCP server, read-only)</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -1139,17 +1139,15 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>192.168.0.128:502</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>TBC (meter address on SAU)</t>
-        </is>
+          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Holding (FC03), 2 regs</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
@@ -1157,14 +1155,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+      <c r="K3" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Ready — quality register 1291</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr"/>
@@ -1175,16 +1171,18 @@
           <t>Apparent current L3 N</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="5" t="n">
+        <v>674</v>
+      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Float32 (ABCD)</t>
         </is>
       </c>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>SAU-100 electric meter (LV PV panel)</t>
+          <t>Plant PC data collector (Modbus TCP server, read-only)</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -1194,17 +1192,15 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>192.168.0.128:502</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>TBC (meter address on SAU)</t>
-        </is>
+          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Holding (FC03), 2 regs</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
@@ -1212,14 +1208,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+      <c r="K4" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Ready — quality register 1292</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
@@ -1230,10 +1224,12 @@
           <t>Psum3</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
+      <c r="B5" s="5" t="n">
+        <v>676</v>
+      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Float32 (ABCD)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1243,7 +1239,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>SAU-100 electric meter (LV PV panel)</t>
+          <t>Plant PC data collector (Modbus TCP server, read-only)</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -1253,17 +1249,15 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>192.168.0.128:502</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>TBC (meter address on SAU)</t>
-        </is>
+          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Holding (FC03), 2 regs</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
@@ -1271,14 +1265,12 @@
           <t>kW</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+      <c r="K5" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Ready — quality register 1293</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr">
@@ -1293,10 +1285,12 @@
           <t>Qsum3</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
+      <c r="B6" s="5" t="n">
+        <v>678</v>
+      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Float32 (ABCD)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1306,7 +1300,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>SAU-100 electric meter (LV PV panel)</t>
+          <t>Plant PC data collector (Modbus TCP server, read-only)</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -1316,17 +1310,15 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>192.168.0.128:502</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>TBC (meter address on SAU)</t>
-        </is>
+          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Holding (FC03), 2 regs</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -1334,14 +1326,12 @@
           <t>kvar</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+      <c r="K6" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Ready — quality register 1294</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
@@ -1352,16 +1342,18 @@
           <t>Real energy L1 L3 delivered</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="5" t="n">
+        <v>680</v>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Float32 (ABCD)</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>SAU-100 electric meter (LV PV panel)</t>
+          <t>Plant PC data collector (Modbus TCP server, read-only)</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -1371,17 +1363,15 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>192.168.0.128:502</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>TBC (meter address on SAU)</t>
-        </is>
+          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Holding (FC03), 2 regs</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -1389,14 +1379,12 @@
           <t>kWh</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+      <c r="K7" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Ready — quality register 1295</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
@@ -1411,16 +1399,18 @@
           <t>Voltage L1 N</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
+      <c r="B8" s="5" t="n">
+        <v>682</v>
+      </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Float32 (ABCD)</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>SAU-100 electric meter (LV PV panel)</t>
+          <t>Plant PC data collector (Modbus TCP server, read-only)</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -1430,17 +1420,15 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>192.168.0.128:502</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>TBC (meter address on SAU)</t>
-        </is>
+          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Holding (FC03), 2 regs</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -1448,14 +1436,12 @@
           <t>V</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+      <c r="K8" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Ready — quality register 1296</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr"/>
@@ -1466,16 +1452,18 @@
           <t>Voltage L2 N</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
+      <c r="B9" s="5" t="n">
+        <v>684</v>
+      </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Float32 (ABCD)</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>SAU-100 electric meter (LV PV panel)</t>
+          <t>Plant PC data collector (Modbus TCP server, read-only)</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -1485,17 +1473,15 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>192.168.0.128:502</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>TBC (meter address on SAU)</t>
-        </is>
+          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Holding (FC03), 2 regs</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -1503,14 +1489,12 @@
           <t>V</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+      <c r="K9" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Ready — quality register 1297</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr"/>
@@ -1521,16 +1505,18 @@
           <t>Voltage L3 N</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
+      <c r="B10" s="5" t="n">
+        <v>686</v>
+      </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Float</t>
+          <t>Float32 (ABCD)</t>
         </is>
       </c>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>SAU-100 electric meter (LV PV panel)</t>
+          <t>Plant PC data collector (Modbus TCP server, read-only)</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1540,17 +1526,15 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>192.168.0.128:502</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>TBC (meter address on SAU)</t>
-        </is>
+          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Holding (FC03), 2 regs</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -1558,14 +1542,12 @@
           <t>V</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+      <c r="K10" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Ready — quality register 1298</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr"/>
@@ -1576,16 +1558,18 @@
           <t>Panel Temperature</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
+      <c r="B11" s="5" t="n">
+        <v>688</v>
+      </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Float32 (ABCD)</t>
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>SAU-100 environmental input (weather station) — TBC</t>
+          <t>Plant PC data collector (Modbus TCP server, read-only)</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -1595,17 +1579,15 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>192.168.0.128:502</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Holding (FC03), 2 regs</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
@@ -1613,14 +1595,12 @@
           <t>°C</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+      <c r="K11" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Ready — quality register 1299</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -1635,16 +1615,18 @@
           <t>Pyranometer</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n"/>
+      <c r="B12" s="5" t="n">
+        <v>690</v>
+      </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Float32 (ABCD)</t>
         </is>
       </c>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>SAU-100 environmental input (weather station) — TBC</t>
+          <t>Plant PC data collector (Modbus TCP server, read-only)</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -1654,17 +1636,15 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>192.168.0.128:502</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Holding (FC03), 2 regs</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -1672,14 +1652,12 @@
           <t>W/m²</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+      <c r="K12" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Ready — quality register 1300</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
@@ -1694,16 +1672,18 @@
           <t>Area_Connection_Error</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
+      <c r="B13" s="5" t="n">
+        <v>692</v>
+      </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Boolean (uint16 0/1)</t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>ComAp InteliNeo 5500</t>
+          <t>Plant PC data collector (Modbus TCP server, read-only)</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -1713,28 +1693,24 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>192.168.0.112:502</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>TBC (InteliNeo Modbus address)</t>
-        </is>
+          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Holding (FC03), 1 reg</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr"/>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+      <c r="K13" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Ready — quality register 1301</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
@@ -1749,16 +1725,18 @@
           <t>Thermal_Magnetic_Switch_On_(LV PANEL)</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
+      <c r="B14" s="5" t="n">
+        <v>693</v>
+      </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Boolean (uint16 0/1)</t>
         </is>
       </c>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>ComAp InteliNeo 5500</t>
+          <t>Plant PC data collector (Modbus TCP server, read-only)</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -1768,28 +1746,24 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>192.168.0.112:502</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>TBC (InteliNeo Modbus address)</t>
-        </is>
+          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Holding (FC03), 1 reg</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr"/>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+      <c r="K14" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Ready — quality register 1302</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
@@ -1804,16 +1778,18 @@
           <t>Thermal_Magnetic_Switch_Off (LV PANEL)</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
+      <c r="B15" s="5" t="n">
+        <v>694</v>
+      </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Boolean (uint16 0/1)</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>ComAp InteliNeo 5500</t>
+          <t>Plant PC data collector (Modbus TCP server, read-only)</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -1823,28 +1799,24 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>192.168.0.112:502</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>TBC (InteliNeo Modbus address)</t>
-        </is>
+          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Holding (FC03), 1 reg</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr"/>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+      <c r="K15" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Ready — quality register 1303</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
@@ -1859,16 +1831,18 @@
           <t>Total_Energy</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n"/>
+      <c r="B16" s="5" t="n">
+        <v>695</v>
+      </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Float32 (ABCD)</t>
         </is>
       </c>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>SAU-100 electric meter (LV PV panel)</t>
+          <t>Plant PC data collector (Modbus TCP server, read-only)</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -1878,17 +1852,15 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>192.168.0.128:502</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>TBC (meter address on SAU)</t>
-        </is>
+          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Holding (FC03), 2 regs</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -1896,14 +1868,12 @@
           <t>kWh</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
+      <c r="K16" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Ready — quality register 1304</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">

--- a/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
+++ b/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>Ready — quality register 1290</t>
+          <t>Pending - no such device on site yet - quality register 1290</t>
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>Ready — quality register 1291</t>
+          <t>Pending - no such device on site yet - quality register 1291</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr"/>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>Ready — quality register 1292</t>
+          <t>Pending - no such device on site yet - quality register 1292</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>Ready — quality register 1293</t>
+          <t>Ready - quality register 1293</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>Ready — quality register 1294</t>
+          <t>Ready - quality register 1294</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>Ready — quality register 1295</t>
+          <t>Pending - no such device on site yet - quality register 1295</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>Ready — quality register 1296</t>
+          <t>Ready - quality register 1296</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr"/>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>Ready — quality register 1297</t>
+          <t>Ready - quality register 1297</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr"/>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>Ready — quality register 1298</t>
+          <t>Ready - quality register 1298</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>Ready — quality register 1299</t>
+          <t>Pending - no such device on site yet - quality register 1299</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>Ready — quality register 1300</t>
+          <t>Pending - no such device on site yet - quality register 1300</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>Ready — quality register 1301</t>
+          <t>Ready - quality register 1301</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>Ready — quality register 1302</t>
+          <t>Ready - quality register 1302</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>Ready — quality register 1303</t>
+          <t>Ready - quality register 1303</t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>Ready — quality register 1304</t>
+          <t>Pending - no such device on site yet - quality register 1304</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">

--- a/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
+++ b/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Sineng Electric (inverters) — inverter model: TBC from nameplate</t>
+          <t>Sineng Electric - 10 x SP-320K-H string inverters, 320 kW each, 12 string inputs (3.2 MW), through a Sineng SAU-100 gateway</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>10 string inverters (template extended from 8 to 10)</t>
+          <t>10 string inverters (winding 1 INV#1-5, winding 2 INV#1-5)</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Electric meter(s) and PID device(s) configured in SAU (seen in SAU device list) — details TBC</t>
+          <t>Two energy meters (generator feeder, grid feeder), a PID device, a relay/RTU. No PV-side energy meter and no pyranometer / module temperature sensor on site.</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>InteliNeo 5500 — Modbus TCP server; register list to be exported from InteliConfig (Modules → Modbus Registers). Gensets: 5 ComAp genset controllers; grid: 3 InteliMains 210</t>
+          <t>InteliNeo 5500 (192.168.0.112, firmware 1.2.0.43) - Modbus TCP server, unit id 1; register table exported from the controller on 2026-10-14. Gensets: 5 x IG4 200; grid: 3 x InteliMains 210 G2</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Local LAN only today. The SAU Modbus server is already at its limit (send-queue congestion, comm-fail events in InteliNeo history, Oct 2026). ANY NEW POLLING OF THE SAU OR INTELINEO MUST BE COORDINATED — see NOTES</t>
+          <t>The plant PC reads the InteliNeo and the SAU once per hour (read-only) and serves this list on its own Modbus TCP server. The platform connects to the plant PC only, never to the field devices.</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>InteliNeo history exports, SAU diagnostics screenshots, integrator site-visit report (Stromatik, 28.09.2026). Still needed: Sineng inverter Modbus map, SAU point table, InteliConfig register export, single-line diagram</t>
+          <t>InteliNeo Modbus register table (2026-10-14), SAU device/signal export, InteliNeo history exports, integrator site-visit report (28.09.2026). Still needed: the SAU-100 Modbus TCP point table for the inverter signals</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Rev.1.2 — structure and known values completed; register addresses marked TBC pending SAU point table and InteliConfig export</t>
+          <t>Rev.1.2 - 2026-10-14: PLC addresses are the plant-PC Modbus server addresses (fixed). Status column: Ready / Pending per tag.</t>
         </is>
       </c>
     </row>
@@ -2103,14 +2103,14 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Yellow cells = value still to be confirmed (TBC). Green cells = confirmed from the site.</t>
+          <t>Status column: Ready = the source signal is wired on site; Pending = the address is fixed but the value stays at quality 0 until the source device is mapped (inverters: SAU point table) or exists (PV-side meter, pyranometer, module temperature).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>PLC_Address / Register = Modbus register on the source device. Convention: Modbus TCP, holding registers (FC03) unless stated; address as listed in the vendor point table (state 0-based or 1-based in Notes when known).</t>
+          <t>PLC_Address = the holding-register address on the plant-PC Modbus server (0-based, FC03). It is fixed and does not change when the site-side device registers are mapped.</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>The 290 inverter tags (10 inverters × 29 signals) should be read in block reads per inverter, at ≥ 10 s interval, not tag-by-tag.</t>
+          <t>Please poll the plant-PC server every 30-60 minutes in block reads (e.g. 100-699 and 1000-1304 in a few requests). The values refresh once per hour; the header registers 0-2 give the time of the last site read.</t>
         </is>
       </c>
     </row>

--- a/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
+++ b/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
@@ -1099,14 +1099,10 @@
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>Pending - no such device on site yet - quality register 1290</t>
-        </is>
-      </c>
-      <c r="M2" s="8" t="inlineStr">
-        <is>
-          <t>Confirm official metering point: SAU meter or InteliNeo PV measurement</t>
-        </is>
-      </c>
+          <t>Pending commissioning - quality register 1290</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1160,10 +1156,10 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>Pending - no such device on site yet - quality register 1291</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr"/>
+          <t>Pending commissioning - quality register 1291</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1213,10 +1209,10 @@
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>Pending - no such device on site yet - quality register 1292</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr"/>
+          <t>Pending commissioning - quality register 1292</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1273,11 +1269,7 @@
           <t>Ready - quality register 1293</t>
         </is>
       </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>Also available in InteliNeo as 'PV prod' (sum of both logger groups)</t>
-        </is>
-      </c>
+      <c r="M5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1334,7 +1326,7 @@
           <t>Ready - quality register 1294</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr"/>
+      <c r="M6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1384,14 +1376,10 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>Pending - no such device on site yet - quality register 1295</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>Cumulative delivered energy; check 32-bit word order</t>
-        </is>
-      </c>
+          <t>Pending commissioning - quality register 1295</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1444,7 +1432,7 @@
           <t>Ready - quality register 1296</t>
         </is>
       </c>
-      <c r="M8" s="8" t="inlineStr"/>
+      <c r="M8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1497,7 +1485,7 @@
           <t>Ready - quality register 1297</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr"/>
+      <c r="M9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1550,7 +1538,7 @@
           <t>Ready - quality register 1298</t>
         </is>
       </c>
-      <c r="M10" s="8" t="inlineStr"/>
+      <c r="M10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1600,14 +1588,10 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>Pending - no such device on site yet - quality register 1299</t>
-        </is>
-      </c>
-      <c r="M11" s="8" t="inlineStr">
-        <is>
-          <t>Confirm sensor exists and where it is wired</t>
-        </is>
-      </c>
+          <t>Pending commissioning - quality register 1299</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1657,14 +1641,10 @@
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>Pending - no such device on site yet - quality register 1300</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t>Confirm sensor exists and where it is wired</t>
-        </is>
-      </c>
+          <t>Pending commissioning - quality register 1300</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1713,11 +1693,7 @@
           <t>Ready - quality register 1301</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t>Suggest: InteliNeo 'PV Logger group 1/2 comm fail' warning bits (OR of both)</t>
-        </is>
-      </c>
+      <c r="M13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1766,11 +1742,7 @@
           <t>Ready - quality register 1302</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t>PVCB closed feedback as read by InteliNeo binary input</t>
-        </is>
-      </c>
+      <c r="M14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1819,11 +1791,7 @@
           <t>Ready - quality register 1303</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
-        <is>
-          <t>PVCB open feedback as read by InteliNeo binary input</t>
-        </is>
-      </c>
+      <c r="M15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1873,14 +1841,10 @@
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>Pending - no such device on site yet - quality register 1304</t>
-        </is>
-      </c>
-      <c r="M16" s="8" t="inlineStr">
-        <is>
-          <t>Alternative: sum of INVn_TOTAL_PRODUCTION; data type 'Word' in template is too small for lifetime kWh — recommend 32-bit</t>
-        </is>
-      </c>
+          <t>Pending commissioning - quality register 1304</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1988,7 +1952,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Two energy meters (generator feeder, grid feeder), a PID device, a relay/RTU. No PV-side energy meter and no pyranometer / module temperature sensor on site.</t>
+          <t>Two energy meters (generator feeder, grid feeder), a PID device, a relay/RTU.</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2012,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>InteliNeo Modbus register table (2026-10-14), SAU device/signal export, InteliNeo history exports, integrator site-visit report (28.09.2026). Still needed: the SAU-100 Modbus TCP point table for the inverter signals</t>
+          <t>InteliNeo Modbus register table (2026-10-14), SAU device/signal export, InteliNeo history exports, integrator site-visit report (28.09.2026).</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2036,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Rev.1.2 - 2026-10-14: PLC addresses are the plant-PC Modbus server addresses (fixed). Status column: Ready / Pending per tag.</t>
+          <t>Rev.1.2 - 2026-10-14: PLC addresses are the plant-PC Modbus server addresses (fixed). Status column: Ready / Pending commissioning per tag.</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2067,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Status column: Ready = the source signal is wired on site; Pending = the address is fixed but the value stays at quality 0 until the source device is mapped (inverters: SAU point table) or exists (PV-side meter, pyranometer, module temperature).</t>
+          <t>Status column: Ready = the source signal is already wired; Pending commissioning = the address is fixed, the value stays at quality 0 until commissioning of that signal is complete.</t>
         </is>
       </c>
     </row>

--- a/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
+++ b/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -142,6 +142,9 @@
     </font>
     <font>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="35">
@@ -510,7 +513,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -528,6 +531,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2051,106 +2055,73 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>How to read this file</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PLC_Address = the holding-register address on the plant-PC Modbus server (0-based, FC03). It is fixed and does not change during commissioning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Float tags: float32, 2 registers, high word first (ABCD), engineering units, scale 1. Boolean tags: one register, 0 / 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Every tag has a quality register (see the register map): 1 = good, 2 = stale, 0 = not available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Status column: Ready = the source signal is already wired; Pending commissioning = the address is fixed, the value stays at quality 0 until commissioning of that signal is complete.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>PLC_Address = the holding-register address on the plant-PC Modbus server (0-based, FC03). It is fixed and does not change when the site-side device registers are mapped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Where the missing addresses come from</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>1. Inverter signals: the Sineng SAU-100 web UI exports the Modbus point table for the connected inverters (Setting → communication / point table). Alternatively the Sineng inverter Modbus protocol document for the installed model. Unit ID per inverter = the inverter's address on the SAU.</t>
-        </is>
-      </c>
-    </row>
+    <row r="6"/>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>2. Plant-level electrical signals (currents, voltages, P, Q, energy): from the electric meter connected to the SAU, or from the InteliNeo 5500 PV/bus measurements — whichever the site confirms as the official metering point.</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Architecture</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>3. Panel temperature / pyranometer: environmental sensors — confirm whether they are wired to the SAU (weather station input) or to another device.</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>One data collector on the plant PC reads the site devices (ComAp InteliNeo 5500 master controller, Sineng SAU-100 gateway) once per hour, read-only, and serves this list on its own Modbus TCP server. The monitoring platform connects to the plant PC only, never to the field devices.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>4. Breaker states (LV panel thermal-magnetic switch): PVCB status as seen by the InteliNeo (binary input) — register from the InteliConfig Modbus register export.</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Please poll the plant-PC server every 30-60 minutes in block reads (e.g. 100-699 and 1000-1304 in a few requests). The header registers 0-2 give the time of the last site read.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>5. ComAp values (PV prod, PV req, bus values, comm status): InteliConfig → Modules → Modbus Registers export of the InteliNeo configuration.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>IMPORTANT for the monitoring integration</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>The SAU Modbus TCP server is single-threaded and is already overloaded by the InteliNeo polling (two sessions, 0 ms pause). Comm-fail events in the InteliNeo cause PV anti-islanding trips and bus under-voltage. Adding another Modbus client directly on the SAU or the InteliNeo will make this worse.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Recommended architecture: ONE local data collector on site reads the SAU and the InteliNeo gently (or reads the SCADA historian) and serves all consumers (DT Turkey monitoring, local dashboards) from its own database/OPC-UA/REST. No second poller on the field devices.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Please poll the plant-PC server every 30-60 minutes in block reads (e.g. 100-699 and 1000-1304 in a few requests). The values refresh once per hour; the header registers 0-2 give the time of the last site read.</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Connection to the plant PC: through the CCI corporate network or a VPN account; the plant's public IP is not opened. Final IP address to follow once the method is agreed.</t>
         </is>
       </c>
     </row>

--- a/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
+++ b/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>InteliNeo Modbus register table (2026-10-14), SAU device/signal export, InteliNeo history exports, integrator site-visit report (28.09.2026).</t>
+          <t>InteliNeo Modbus register table (2026-10-14), SAU device/signal export, InteliNeo history exports.</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Eng. Yousif (site); Sabir (data / monitoring integration); Stromatik Automation, Eng. Salwan (ComAp integrator); Sineng support (via site)</t>
+          <t>Eng. Yousif (site); Sabir (data / monitoring integration)</t>
         </is>
       </c>
     </row>

--- a/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
+++ b/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>SAU local web UI (Device Monitor); ComAp InteliNeo 5500 master controller (IP 192.168.0.112) reads PV as 'PV Logger group 1/2' via Modbus TCP, unit address 245; plant SCADA PC; no cloud platform confirmed</t>
+          <t>SAU-100 local web interface (dashboard, device monitor, logs); ComAp InteliConfig on the plant computer for the controllers. The InteliNeo 5500 master controller (192.168.0.112) reads the PV totals from the SAU over Modbus TCP (unit address 245). No cloud platform connected.</t>
         </is>
       </c>
     </row>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Modbus TCP (SAU, InteliNeo); Modbus RTU (inverters ↔ SAU, RS485); ComAp AirGate/WebSupervisor possible for InteliNeo (not enabled yet)</t>
+          <t>Modbus TCP (SAU-100, InteliNeo); Modbus RTU over RS485 (inverters to SAU); the SAU also supports IEC 60870-5-104</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Eng. Yousif (site); Sabir (data / monitoring integration)</t>
+          <t>Sabir Tishko (data / monitoring integration)</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>

--- a/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
+++ b/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
@@ -1380,7 +1380,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>Pending commissioning - quality register 1295</t>
+          <t>Ready - quality register 1295</t>
         </is>
       </c>
       <c r="M7" s="8" t="n"/>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>Pending commissioning - quality register 1304</t>
+          <t>Ready - quality register 1304</t>
         </is>
       </c>
       <c r="M16" s="8" t="n"/>

--- a/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
+++ b/docs/turkey/Solar_Tag_List_Rev.1.2.xlsx
@@ -1082,7 +1082,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+          <t>&lt;plant-pc-ip&gt;:502</t>
         </is>
       </c>
       <c r="H2" s="7" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+          <t>&lt;plant-pc-ip&gt;:502</t>
         </is>
       </c>
       <c r="H3" s="7" t="n">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+          <t>&lt;plant-pc-ip&gt;:502</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+          <t>&lt;plant-pc-ip&gt;:502</t>
         </is>
       </c>
       <c r="H5" s="7" t="n">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+          <t>&lt;plant-pc-ip&gt;:502</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+          <t>&lt;plant-pc-ip&gt;:502</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+          <t>&lt;plant-pc-ip&gt;:502</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+          <t>&lt;plant-pc-ip&gt;:502</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+          <t>&lt;plant-pc-ip&gt;:502</t>
         </is>
       </c>
       <c r="H10" s="7" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+          <t>&lt;plant-pc-ip&gt;:502</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+          <t>&lt;plant-pc-ip&gt;:502</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+          <t>&lt;plant-pc-ip&gt;:502</t>
         </is>
       </c>
       <c r="H13" s="7" t="n">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+          <t>&lt;plant-pc-ip&gt;:502</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+          <t>&lt;plant-pc-ip&gt;:502</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>&lt;plant-pc-vpn-ip&gt;:502</t>
+          <t>&lt;plant-pc-ip&gt;:502</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
